--- a/data/nzd0493/nzd0493.xlsx
+++ b/data/nzd0493/nzd0493.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L699"/>
+  <dimension ref="A1:L705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29780,6 +29780,258 @@
         <v>348.12</v>
       </c>
       <c r="L699" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>181.06</v>
+      </c>
+      <c r="C700" t="n">
+        <v>315.41</v>
+      </c>
+      <c r="D700" t="n">
+        <v>314.64</v>
+      </c>
+      <c r="E700" t="n">
+        <v>311.97</v>
+      </c>
+      <c r="F700" t="n">
+        <v>320.45</v>
+      </c>
+      <c r="G700" t="n">
+        <v>326.08</v>
+      </c>
+      <c r="H700" t="n">
+        <v>330.08</v>
+      </c>
+      <c r="I700" t="n">
+        <v>338.51</v>
+      </c>
+      <c r="J700" t="n">
+        <v>341.42</v>
+      </c>
+      <c r="K700" t="n">
+        <v>347.87</v>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:10+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>181.06</v>
+      </c>
+      <c r="C701" t="n">
+        <v>330.84</v>
+      </c>
+      <c r="D701" t="n">
+        <v>320.77</v>
+      </c>
+      <c r="E701" t="n">
+        <v>314.38</v>
+      </c>
+      <c r="F701" t="n">
+        <v>319.56</v>
+      </c>
+      <c r="G701" t="n">
+        <v>326.08</v>
+      </c>
+      <c r="H701" t="n">
+        <v>330.08</v>
+      </c>
+      <c r="I701" t="n">
+        <v>338.51</v>
+      </c>
+      <c r="J701" t="n">
+        <v>341.42</v>
+      </c>
+      <c r="K701" t="n">
+        <v>350.22</v>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>168.99</v>
+      </c>
+      <c r="C702" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="D702" t="n">
+        <v>320.67</v>
+      </c>
+      <c r="E702" t="n">
+        <v>314.32</v>
+      </c>
+      <c r="F702" t="n">
+        <v>320.05</v>
+      </c>
+      <c r="G702" t="n">
+        <v>326.34</v>
+      </c>
+      <c r="H702" t="n">
+        <v>329.78</v>
+      </c>
+      <c r="I702" t="n">
+        <v>339.08</v>
+      </c>
+      <c r="J702" t="n">
+        <v>341.55</v>
+      </c>
+      <c r="K702" t="n">
+        <v>350.81</v>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>167.06</v>
+      </c>
+      <c r="C703" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="D703" t="n">
+        <v>320.67</v>
+      </c>
+      <c r="E703" t="n">
+        <v>314.25</v>
+      </c>
+      <c r="F703" t="n">
+        <v>319.83</v>
+      </c>
+      <c r="G703" t="n">
+        <v>326.37</v>
+      </c>
+      <c r="H703" t="n">
+        <v>329.72</v>
+      </c>
+      <c r="I703" t="n">
+        <v>338.37</v>
+      </c>
+      <c r="J703" t="n">
+        <v>340.96</v>
+      </c>
+      <c r="K703" t="n">
+        <v>350.63</v>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>165.73</v>
+      </c>
+      <c r="C704" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="D704" t="n">
+        <v>320.67</v>
+      </c>
+      <c r="E704" t="n">
+        <v>313.28</v>
+      </c>
+      <c r="F704" t="n">
+        <v>319.1</v>
+      </c>
+      <c r="G704" t="n">
+        <v>325.91</v>
+      </c>
+      <c r="H704" t="n">
+        <v>329.02</v>
+      </c>
+      <c r="I704" t="n">
+        <v>337.88</v>
+      </c>
+      <c r="J704" t="n">
+        <v>340.16</v>
+      </c>
+      <c r="K704" t="n">
+        <v>349.6</v>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>165.73</v>
+      </c>
+      <c r="C705" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="D705" t="n">
+        <v>320.67</v>
+      </c>
+      <c r="E705" t="n">
+        <v>313.28</v>
+      </c>
+      <c r="F705" t="n">
+        <v>319.1</v>
+      </c>
+      <c r="G705" t="n">
+        <v>325.91</v>
+      </c>
+      <c r="H705" t="n">
+        <v>328.88</v>
+      </c>
+      <c r="I705" t="n">
+        <v>337.6</v>
+      </c>
+      <c r="J705" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="K705" t="n">
+        <v>349.32</v>
+      </c>
+      <c r="L705" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29796,7 +30048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B729"/>
+  <dimension ref="A1:B735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37089,6 +37341,66 @@
       </c>
       <c r="B729" t="n">
         <v>0.46</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -37257,28 +37569,28 @@
         <v>0.1115</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.074896729707986</v>
+        <v>-1.218280781597987</v>
       </c>
       <c r="J2" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="K2" t="n">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01791551993819485</v>
+        <v>0.02292377728227035</v>
       </c>
       <c r="M2" t="n">
-        <v>47.4795289594152</v>
+        <v>47.71035163346283</v>
       </c>
       <c r="N2" t="n">
-        <v>2959.162126731403</v>
+        <v>2985.300000011007</v>
       </c>
       <c r="O2" t="n">
-        <v>54.39818128146752</v>
+        <v>54.63789893481453</v>
       </c>
       <c r="P2" t="n">
-        <v>278.5769278888338</v>
+        <v>280.3242488913989</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37335,28 +37647,28 @@
         <v>0.0825</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3440626489404776</v>
+        <v>-0.3411772700755175</v>
       </c>
       <c r="J3" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="K3" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="L3" t="n">
-        <v>0.130960167637488</v>
+        <v>0.1302586739878604</v>
       </c>
       <c r="M3" t="n">
-        <v>4.892642097768827</v>
+        <v>4.894212567473238</v>
       </c>
       <c r="N3" t="n">
-        <v>38.39214210569538</v>
+        <v>38.35670402930711</v>
       </c>
       <c r="O3" t="n">
-        <v>6.196139290372303</v>
+        <v>6.193278940053251</v>
       </c>
       <c r="P3" t="n">
-        <v>335.6043136403254</v>
+        <v>335.5699942246689</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37413,28 +37725,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3808960500778246</v>
+        <v>-0.3757318675928115</v>
       </c>
       <c r="J4" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="K4" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1622861756196939</v>
+        <v>0.1606407978039081</v>
       </c>
       <c r="M4" t="n">
-        <v>4.791893813855615</v>
+        <v>4.781464743917997</v>
       </c>
       <c r="N4" t="n">
-        <v>36.60108175278157</v>
+        <v>36.40371573436541</v>
       </c>
       <c r="O4" t="n">
-        <v>6.049882788350661</v>
+        <v>6.033549182228103</v>
       </c>
       <c r="P4" t="n">
-        <v>327.0010014815719</v>
+        <v>326.9397084463979</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37491,28 +37803,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3045376963962909</v>
+        <v>-0.3123177384997292</v>
       </c>
       <c r="J5" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="K5" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1086106823639813</v>
+        <v>0.1149847309612515</v>
       </c>
       <c r="M5" t="n">
-        <v>4.844150445426432</v>
+        <v>4.84114688663025</v>
       </c>
       <c r="N5" t="n">
-        <v>37.20007592603489</v>
+        <v>37.0511370964571</v>
       </c>
       <c r="O5" t="n">
-        <v>6.099186497069498</v>
+        <v>6.086964522358997</v>
       </c>
       <c r="P5" t="n">
-        <v>326.1874155404522</v>
+        <v>326.2796914409289</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37569,28 +37881,28 @@
         <v>0.0944</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3430896200999178</v>
+        <v>-0.3506316776072735</v>
       </c>
       <c r="J6" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="K6" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1816672643190057</v>
+        <v>0.1901132539235779</v>
       </c>
       <c r="M6" t="n">
-        <v>4.098790383137534</v>
+        <v>4.099731935576988</v>
       </c>
       <c r="N6" t="n">
-        <v>25.91404645719376</v>
+        <v>25.84710124825039</v>
       </c>
       <c r="O6" t="n">
-        <v>5.090584097841206</v>
+        <v>5.084004450062017</v>
       </c>
       <c r="P6" t="n">
-        <v>333.1888133343113</v>
+        <v>333.2782815822798</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37647,28 +37959,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2269047668094723</v>
+        <v>-0.2334800356072797</v>
       </c>
       <c r="J7" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="K7" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1338602254697098</v>
+        <v>0.1419770947845541</v>
       </c>
       <c r="M7" t="n">
-        <v>3.217679643273843</v>
+        <v>3.220162524156473</v>
       </c>
       <c r="N7" t="n">
-        <v>16.28135314607846</v>
+        <v>16.25839784233506</v>
       </c>
       <c r="O7" t="n">
-        <v>4.035015879284548</v>
+        <v>4.032170363753876</v>
       </c>
       <c r="P7" t="n">
-        <v>335.9472249378404</v>
+        <v>336.0252175632777</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37725,28 +38037,28 @@
         <v>0.1156</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09449693370774857</v>
+        <v>-0.1028557724100907</v>
       </c>
       <c r="J8" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="K8" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03747498598882548</v>
+        <v>0.04415522212144385</v>
       </c>
       <c r="M8" t="n">
-        <v>2.707292684732709</v>
+        <v>2.720486758022448</v>
       </c>
       <c r="N8" t="n">
-        <v>11.20915321031233</v>
+        <v>11.30212968149313</v>
       </c>
       <c r="O8" t="n">
-        <v>3.348007349202258</v>
+        <v>3.361864018887905</v>
       </c>
       <c r="P8" t="n">
-        <v>336.8787397306321</v>
+        <v>336.9778974266224</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37803,28 +38115,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05877104691323379</v>
+        <v>-0.06089694357739402</v>
       </c>
       <c r="J9" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="K9" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01289899044191645</v>
+        <v>0.01407269541691381</v>
       </c>
       <c r="M9" t="n">
-        <v>2.868781089703336</v>
+        <v>2.855973338128678</v>
       </c>
       <c r="N9" t="n">
-        <v>12.91812718171068</v>
+        <v>12.82201398587878</v>
       </c>
       <c r="O9" t="n">
-        <v>3.594179625687993</v>
+        <v>3.580783990396347</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1145552320149</v>
+        <v>341.1397785064437</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37881,28 +38193,28 @@
         <v>0.1026</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04728212097558261</v>
+        <v>0.04579586434283604</v>
       </c>
       <c r="J10" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="K10" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01119321277908447</v>
+        <v>0.01068938812454967</v>
       </c>
       <c r="M10" t="n">
-        <v>2.486514382116718</v>
+        <v>2.472516404918283</v>
       </c>
       <c r="N10" t="n">
-        <v>9.652002051250157</v>
+        <v>9.579216525290581</v>
       </c>
       <c r="O10" t="n">
-        <v>3.106767138240354</v>
+        <v>3.09503094092621</v>
       </c>
       <c r="P10" t="n">
-        <v>340.470831405667</v>
+        <v>340.4884733134998</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37959,28 +38271,28 @@
         <v>0.1391</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06379367093657229</v>
+        <v>0.07099400906565315</v>
       </c>
       <c r="J11" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="K11" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02201420064300519</v>
+        <v>0.02716625700939312</v>
       </c>
       <c r="M11" t="n">
-        <v>2.374316941763314</v>
+        <v>2.388874495957349</v>
       </c>
       <c r="N11" t="n">
-        <v>8.835917306829346</v>
+        <v>8.907377787576136</v>
       </c>
       <c r="O11" t="n">
-        <v>2.972527091016892</v>
+        <v>2.984523041890636</v>
       </c>
       <c r="P11" t="n">
-        <v>343.9394955738852</v>
+        <v>343.8540800958364</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38018,7 +38330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L699"/>
+  <dimension ref="A1:L705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81311,6 +81623,378 @@
         </is>
       </c>
     </row>
+    <row r="700">
+      <c r="A700" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>-45.529374404176245,170.7598337164615</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>-45.530776092210196,170.75968632553906</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>-45.531303411789764,170.7591211003883</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>-45.531707067716624,170.75849079065657</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>-45.53218182888267,170.75789718690484</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>-45.53265563750403,170.75728931527655</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>-45.533132454883614,170.7566925986402</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>-45.53364691234133,170.75615558538766</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>-45.53416962837388,170.75565333276944</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>-45.53471989203851,170.7552068558726</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:10+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>-45.529374404176245,170.7598337164615</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>-45.5308840259731,170.75981056837517</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>-45.53133999906671,170.75917982532266</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>-45.53172311606832,170.75851153967938</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>-45.53217584192969,170.7578896199699</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>-45.53265563750403,170.75728931527655</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>-45.533132454883614,170.7566925986402</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>-45.53364691234133,170.75615558538766</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>-45.53416962837388,170.75565333276944</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>-45.53473229997468,170.75523121750405</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>-45.52927591251431,170.7597686131882</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>-45.53088094814884,170.75980702547503</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>-45.531339402210875,170.75917886732964</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>-45.531722716524335,170.75851102310605</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>-45.532179138117336,170.757893786035</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>-45.53265733616208,170.75729160395088</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>-45.53313055218496,170.7566898743346</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>-45.53365026010701,170.75616111369993</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>-45.53417032691471,170.7556546677277</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>-45.53473541515785,170.75523733383025</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>-45.52926016363725,170.75975820315765</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>-45.53088094814884,170.75980702547503</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>-45.531339402210875,170.75917886732964</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>-45.531722250389684,170.75851042043718</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>-45.53217765819638,170.75789191555674</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>-45.53265753216108,170.75729186802872</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>-45.53313017164521,170.75668932947352</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>-45.53364609008305,170.7561542275567</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>-45.53416715661392,170.75564860907133</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>-45.53473446476302,170.75523546783234</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>-45.529249310783634,170.75975102940933</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>-45.53088094814884,170.75980702547503</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>-45.531339402210875,170.75917886732964</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>-45.53171579109495,170.75850206916957</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>-45.532172747549325,170.75788570897043</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>-45.53265452684296,170.75728781883572</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>-45.53312573201472,170.7566829727612</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>-45.53364321217897,170.75614947514856</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>-45.53416285790049,170.7556403939452</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>-45.534729026392,170.75522479017894</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>-45.529249310783634,170.75975102940933</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>-45.53088094814884,170.75980702547503</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>-45.531339402210875,170.75917886732964</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>-45.53171579109495,170.75850206916957</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>-45.532172747549325,170.75788570897043</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>-45.53265452684296,170.75728781883572</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>-45.5331248440886,170.75668170141887</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>-45.53364156766226,170.75614675948702</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>-45.534161460818495,170.75563772402947</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>-45.534727547999715,170.75522188751626</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0493/nzd0493.xlsx
+++ b/data/nzd0493/nzd0493.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L705"/>
+  <dimension ref="A1:L710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29837,10 +29837,10 @@
         <v>181.06</v>
       </c>
       <c r="C701" t="n">
-        <v>330.84</v>
+        <v>315.41</v>
       </c>
       <c r="D701" t="n">
-        <v>320.77</v>
+        <v>314.64</v>
       </c>
       <c r="E701" t="n">
         <v>314.38</v>
@@ -29879,10 +29879,10 @@
         <v>168.99</v>
       </c>
       <c r="C702" t="n">
-        <v>330.4</v>
+        <v>312.71</v>
       </c>
       <c r="D702" t="n">
-        <v>320.67</v>
+        <v>313.92</v>
       </c>
       <c r="E702" t="n">
         <v>314.32</v>
@@ -29921,10 +29921,10 @@
         <v>167.06</v>
       </c>
       <c r="C703" t="n">
-        <v>330.4</v>
+        <v>312.71</v>
       </c>
       <c r="D703" t="n">
-        <v>320.67</v>
+        <v>313.92</v>
       </c>
       <c r="E703" t="n">
         <v>314.25</v>
@@ -29963,10 +29963,10 @@
         <v>165.73</v>
       </c>
       <c r="C704" t="n">
-        <v>330.4</v>
+        <v>312.71</v>
       </c>
       <c r="D704" t="n">
-        <v>320.67</v>
+        <v>313.92</v>
       </c>
       <c r="E704" t="n">
         <v>313.28</v>
@@ -30005,10 +30005,10 @@
         <v>165.73</v>
       </c>
       <c r="C705" t="n">
-        <v>330.4</v>
+        <v>312.71</v>
       </c>
       <c r="D705" t="n">
-        <v>320.67</v>
+        <v>313.92</v>
       </c>
       <c r="E705" t="n">
         <v>313.28</v>
@@ -30032,6 +30032,216 @@
         <v>349.32</v>
       </c>
       <c r="L705" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:14:11+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>168.99</v>
+      </c>
+      <c r="C706" t="n">
+        <v>312.82</v>
+      </c>
+      <c r="D706" t="n">
+        <v>312.71</v>
+      </c>
+      <c r="E706" t="n">
+        <v>312.67</v>
+      </c>
+      <c r="F706" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="G706" t="n">
+        <v>325.48</v>
+      </c>
+      <c r="H706" t="n">
+        <v>328.42</v>
+      </c>
+      <c r="I706" t="n">
+        <v>337.18</v>
+      </c>
+      <c r="J706" t="n">
+        <v>339.29</v>
+      </c>
+      <c r="K706" t="n">
+        <v>348.77</v>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:01+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>169.68</v>
+      </c>
+      <c r="C707" t="n">
+        <v>312.82</v>
+      </c>
+      <c r="D707" t="n">
+        <v>312.55</v>
+      </c>
+      <c r="E707" t="n">
+        <v>312.97</v>
+      </c>
+      <c r="F707" t="n">
+        <v>318.87</v>
+      </c>
+      <c r="G707" t="n">
+        <v>325.57</v>
+      </c>
+      <c r="H707" t="n">
+        <v>328.18</v>
+      </c>
+      <c r="I707" t="n">
+        <v>337.47</v>
+      </c>
+      <c r="J707" t="n">
+        <v>339.29</v>
+      </c>
+      <c r="K707" t="n">
+        <v>348.29</v>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>168.64</v>
+      </c>
+      <c r="C708" t="n">
+        <v>312.82</v>
+      </c>
+      <c r="D708" t="n">
+        <v>312.32</v>
+      </c>
+      <c r="E708" t="n">
+        <v>313.49</v>
+      </c>
+      <c r="F708" t="n">
+        <v>319.07</v>
+      </c>
+      <c r="G708" t="n">
+        <v>325.34</v>
+      </c>
+      <c r="H708" t="n">
+        <v>327.88</v>
+      </c>
+      <c r="I708" t="n">
+        <v>337.14</v>
+      </c>
+      <c r="J708" t="n">
+        <v>339.34</v>
+      </c>
+      <c r="K708" t="n">
+        <v>347.82</v>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:08+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>169.77</v>
+      </c>
+      <c r="C709" t="n">
+        <v>314.02</v>
+      </c>
+      <c r="D709" t="n">
+        <v>313.08</v>
+      </c>
+      <c r="E709" t="n">
+        <v>314.21</v>
+      </c>
+      <c r="F709" t="n">
+        <v>319.29</v>
+      </c>
+      <c r="G709" t="n">
+        <v>325.8</v>
+      </c>
+      <c r="H709" t="n">
+        <v>328.38</v>
+      </c>
+      <c r="I709" t="n">
+        <v>337.63</v>
+      </c>
+      <c r="J709" t="n">
+        <v>339.52</v>
+      </c>
+      <c r="K709" t="n">
+        <v>347.96</v>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>169.46</v>
+      </c>
+      <c r="C710" t="n">
+        <v>314.21</v>
+      </c>
+      <c r="D710" t="n">
+        <v>313.35</v>
+      </c>
+      <c r="E710" t="n">
+        <v>314.6</v>
+      </c>
+      <c r="F710" t="n">
+        <v>319.2</v>
+      </c>
+      <c r="G710" t="n">
+        <v>326.02</v>
+      </c>
+      <c r="H710" t="n">
+        <v>328.63</v>
+      </c>
+      <c r="I710" t="n">
+        <v>337.85</v>
+      </c>
+      <c r="J710" t="n">
+        <v>339.52</v>
+      </c>
+      <c r="K710" t="n">
+        <v>347.83</v>
+      </c>
+      <c r="L710" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30048,7 +30258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B735"/>
+  <dimension ref="A1:B740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37401,6 +37611,56 @@
       </c>
       <c r="B735" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -37569,28 +37829,28 @@
         <v>0.1115</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.218280781597987</v>
+        <v>-1.33610473529806</v>
       </c>
       <c r="J2" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="K2" t="n">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02292377728227035</v>
+        <v>0.0274700232836772</v>
       </c>
       <c r="M2" t="n">
-        <v>47.71035163346283</v>
+        <v>47.88859997199668</v>
       </c>
       <c r="N2" t="n">
-        <v>2985.300000011007</v>
+        <v>3006.725235056258</v>
       </c>
       <c r="O2" t="n">
-        <v>54.63789893481453</v>
+        <v>54.8336140980718</v>
       </c>
       <c r="P2" t="n">
-        <v>280.3242488913989</v>
+        <v>281.7641201509576</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37647,28 +37907,28 @@
         <v>0.0825</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3411772700755175</v>
+        <v>-0.384813945050798</v>
       </c>
       <c r="J3" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="K3" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1302586739878604</v>
+        <v>0.1546857917304866</v>
       </c>
       <c r="M3" t="n">
-        <v>4.894212567473238</v>
+        <v>5.032761038180118</v>
       </c>
       <c r="N3" t="n">
-        <v>38.35670402930711</v>
+        <v>40.25331530785397</v>
       </c>
       <c r="O3" t="n">
-        <v>6.193278940053251</v>
+        <v>6.344550047706612</v>
       </c>
       <c r="P3" t="n">
-        <v>335.5699942246689</v>
+        <v>336.0883477823325</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37725,28 +37985,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3757318675928115</v>
+        <v>-0.3910447456136834</v>
       </c>
       <c r="J4" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="K4" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1606407978039081</v>
+        <v>0.1736663327541962</v>
       </c>
       <c r="M4" t="n">
-        <v>4.781464743917997</v>
+        <v>4.766368676444427</v>
       </c>
       <c r="N4" t="n">
-        <v>36.40371573436541</v>
+        <v>36.19303733106343</v>
       </c>
       <c r="O4" t="n">
-        <v>6.033549182228103</v>
+        <v>6.016064937404136</v>
       </c>
       <c r="P4" t="n">
-        <v>326.9397084463979</v>
+        <v>327.1215790418112</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37803,28 +38063,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3123177384997292</v>
+        <v>-0.3184880175130588</v>
       </c>
       <c r="J5" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="K5" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1149847309612515</v>
+        <v>0.1202354443888488</v>
       </c>
       <c r="M5" t="n">
-        <v>4.84114688663025</v>
+        <v>4.837523299612479</v>
       </c>
       <c r="N5" t="n">
-        <v>37.0511370964571</v>
+        <v>36.91921433258288</v>
       </c>
       <c r="O5" t="n">
-        <v>6.086964522358997</v>
+        <v>6.076118360646283</v>
       </c>
       <c r="P5" t="n">
-        <v>326.2796914409289</v>
+        <v>326.3530859850183</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37881,28 +38141,28 @@
         <v>0.0944</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3506316776072735</v>
+        <v>-0.3576247360566228</v>
       </c>
       <c r="J6" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="K6" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1901132539235779</v>
+        <v>0.1976454838529071</v>
       </c>
       <c r="M6" t="n">
-        <v>4.099731935576988</v>
+        <v>4.104313191302175</v>
       </c>
       <c r="N6" t="n">
-        <v>25.84710124825039</v>
+        <v>25.82657488953532</v>
       </c>
       <c r="O6" t="n">
-        <v>5.084004450062017</v>
+        <v>5.081985329527754</v>
       </c>
       <c r="P6" t="n">
-        <v>333.2782815822798</v>
+        <v>333.3614728230672</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37959,28 +38219,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2334800356072797</v>
+        <v>-0.239389140703502</v>
       </c>
       <c r="J7" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="K7" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1419770947845541</v>
+        <v>0.1491706831037481</v>
       </c>
       <c r="M7" t="n">
-        <v>3.220162524156473</v>
+        <v>3.223951531259045</v>
       </c>
       <c r="N7" t="n">
-        <v>16.25839784233506</v>
+        <v>16.25923718002112</v>
       </c>
       <c r="O7" t="n">
-        <v>4.032170363753876</v>
+        <v>4.032274442547421</v>
       </c>
       <c r="P7" t="n">
-        <v>336.0252175632777</v>
+        <v>336.09551395969</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38037,28 +38297,28 @@
         <v>0.1156</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1028557724100907</v>
+        <v>-0.1113978058471085</v>
       </c>
       <c r="J8" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="K8" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04415522212144385</v>
+        <v>0.05109728752277565</v>
       </c>
       <c r="M8" t="n">
-        <v>2.720486758022448</v>
+        <v>2.73882608208078</v>
       </c>
       <c r="N8" t="n">
-        <v>11.30212968149313</v>
+        <v>11.46329378012631</v>
       </c>
       <c r="O8" t="n">
-        <v>3.361864018887905</v>
+        <v>3.385748629199502</v>
       </c>
       <c r="P8" t="n">
-        <v>336.9778974266224</v>
+        <v>337.0795192228656</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38115,28 +38375,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06089694357739402</v>
+        <v>-0.06385586571209907</v>
       </c>
       <c r="J9" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="K9" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01407269541691381</v>
+        <v>0.01564593640574641</v>
       </c>
       <c r="M9" t="n">
-        <v>2.855973338128678</v>
+        <v>2.851826036922729</v>
       </c>
       <c r="N9" t="n">
-        <v>12.82201398587878</v>
+        <v>12.7609697550901</v>
       </c>
       <c r="O9" t="n">
-        <v>3.580783990396347</v>
+        <v>3.57224995697251</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1397785064437</v>
+        <v>341.1749763508209</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38193,28 +38453,28 @@
         <v>0.1026</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04579586434283604</v>
+        <v>0.04242260644738505</v>
       </c>
       <c r="J10" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="K10" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01068938812454967</v>
+        <v>0.00928765091721051</v>
       </c>
       <c r="M10" t="n">
-        <v>2.472516404918283</v>
+        <v>2.471200340158814</v>
       </c>
       <c r="N10" t="n">
-        <v>9.579216525290581</v>
+        <v>9.549237527810224</v>
       </c>
       <c r="O10" t="n">
-        <v>3.09503094092621</v>
+        <v>3.090184060506789</v>
       </c>
       <c r="P10" t="n">
-        <v>340.4884733134998</v>
+        <v>340.5286029004625</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38271,28 +38531,28 @@
         <v>0.1391</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07099400906565315</v>
+        <v>0.07441575316578446</v>
       </c>
       <c r="J11" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="K11" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02716625700939312</v>
+        <v>0.0300737881939428</v>
       </c>
       <c r="M11" t="n">
-        <v>2.388874495957349</v>
+        <v>2.388813489949528</v>
       </c>
       <c r="N11" t="n">
-        <v>8.907377787576136</v>
+        <v>8.884083462878255</v>
       </c>
       <c r="O11" t="n">
-        <v>2.984523041890636</v>
+        <v>2.980617966609987</v>
       </c>
       <c r="P11" t="n">
-        <v>343.8540800958364</v>
+        <v>343.8133766897675</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38330,7 +38590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L705"/>
+  <dimension ref="A1:L710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81698,12 +81958,12 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>-45.5308840259731,170.75981056837517</t>
+          <t>-45.530776092210196,170.75968632553906</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>-45.53133999906671,170.75917982532266</t>
+          <t>-45.531303411789764,170.7591211003883</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
@@ -81760,12 +82020,12 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>-45.53088094814884,170.75980702547503</t>
+          <t>-45.53075720553727,170.75966458510433</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>-45.531339402210875,170.75917886732964</t>
+          <t>-45.53129911442417,170.75911420284802</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
@@ -81822,12 +82082,12 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>-45.53088094814884,170.75980702547503</t>
+          <t>-45.53075720553727,170.75966458510433</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>-45.531339402210875,170.75917886732964</t>
+          <t>-45.53129911442417,170.75911420284802</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
@@ -81884,12 +82144,12 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>-45.53088094814884,170.75980702547503</t>
+          <t>-45.53075720553727,170.75966458510433</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>-45.531339402210875,170.75917886732964</t>
+          <t>-45.53129911442417,170.75911420284802</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
@@ -81946,12 +82206,12 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>-45.53088094814884,170.75980702547503</t>
+          <t>-45.53075720553727,170.75966458510433</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>-45.531339402210875,170.75917886732964</t>
+          <t>-45.53129911442417,170.75911420284802</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
@@ -81990,6 +82250,316 @@
         </is>
       </c>
       <c r="L705" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:14:11+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>-45.52927591251431,170.7597686131882</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>-45.5307579749944,170.7596654708255</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>-45.531291892461645,170.75910261115072</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>-45.531711729063964,170.75849681734246</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>-45.53216871140081,170.75788060766743</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>-45.53265171752374,170.75728403372094</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>-45.533121926616914,170.75667752415146</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>-45.533639100887086,170.75614268599497</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>-45.53415818304899,170.75563145999695</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>-45.53472464401466,170.7552161858578</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:01+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>-45.529281542941646,170.75977233491034</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>-45.5307579749944,170.7596654708255</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>-45.53129093749132,170.75910107836455</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>-45.531713726784155,170.75849940020817</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>-45.53217120035909,170.75788375347088</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>-45.5326523055208,170.75728482595423</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>-45.53312040445771,170.7566753447078</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>-45.533640804136624,170.7561454986442</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>-45.53415818304899,170.75563145999695</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>-45.534722109627474,170.75521120986548</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>-45.529273056500394,170.7597667253584</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>-45.5307579749944,170.7596654708255</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>-45.531289564721426,170.75909887498446</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>-45.53171718949903,170.7585038771758</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>-45.5321725457419,170.7578854539053</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>-45.532650802861646,170.75728280135806</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>-45.53311850175866,170.7566726204033</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>-45.53363886595611,170.75614229804333</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>-45.53415845171863,170.7556319734422</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>-45.53471962803981,170.7552063375401</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:08+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>-45.52928227734519,170.7597728203524</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>-45.53076636907166,170.75967513323937</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>-45.53129410083047,170.759106155719</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>-45.53172198402703,170.75851007605496</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>-45.53217402566296,170.7578873243832</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>-45.53265380817992,170.75728685055049</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>-45.533121672923706,170.75667716091084</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>-45.53364174386049,170.75614705045075</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>-45.53415941892933,170.7556338218452</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>-45.53472036723616,170.75520778887102</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>-45.529279747732936,170.75977114827424</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>-45.530767698133815,170.75967666312184</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>-45.53129571234279,170.759108742296</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>-45.531724581062896,170.75851343378162</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>-45.53217342024072,170.75788655918768</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>-45.53265524550601,170.75728878712096</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>-45.53312325850619,170.75667943116477</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>-45.53364303598075,170.75614918418484</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>-45.53415941892933,170.7556338218452</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>-45.53471968083956,170.75520644120658</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0493/nzd0493.xlsx
+++ b/data/nzd0493/nzd0493.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L710"/>
+  <dimension ref="A1:L713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30242,6 +30242,132 @@
         <v>347.83</v>
       </c>
       <c r="L710" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>169.34</v>
+      </c>
+      <c r="C711" t="n">
+        <v>315.53</v>
+      </c>
+      <c r="D711" t="n">
+        <v>313.68</v>
+      </c>
+      <c r="E711" t="n">
+        <v>314.75</v>
+      </c>
+      <c r="F711" t="n">
+        <v>319.43</v>
+      </c>
+      <c r="G711" t="n">
+        <v>326.34</v>
+      </c>
+      <c r="H711" t="n">
+        <v>329.1</v>
+      </c>
+      <c r="I711" t="n">
+        <v>337.99</v>
+      </c>
+      <c r="J711" t="n">
+        <v>339.79</v>
+      </c>
+      <c r="K711" t="n">
+        <v>347.95</v>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>162.97</v>
+      </c>
+      <c r="C712" t="n">
+        <v>314.34</v>
+      </c>
+      <c r="D712" t="n">
+        <v>315.59</v>
+      </c>
+      <c r="E712" t="n">
+        <v>316.23</v>
+      </c>
+      <c r="F712" t="n">
+        <v>320.13</v>
+      </c>
+      <c r="G712" t="n">
+        <v>326.87</v>
+      </c>
+      <c r="H712" t="n">
+        <v>329.27</v>
+      </c>
+      <c r="I712" t="n">
+        <v>338.35</v>
+      </c>
+      <c r="J712" t="n">
+        <v>339.79</v>
+      </c>
+      <c r="K712" t="n">
+        <v>348.38</v>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>169.44</v>
+      </c>
+      <c r="C713" t="n">
+        <v>314.92</v>
+      </c>
+      <c r="D713" t="n">
+        <v>315.3</v>
+      </c>
+      <c r="E713" t="n">
+        <v>316.33</v>
+      </c>
+      <c r="F713" t="n">
+        <v>320.4</v>
+      </c>
+      <c r="G713" t="n">
+        <v>326.96</v>
+      </c>
+      <c r="H713" t="n">
+        <v>329.66</v>
+      </c>
+      <c r="I713" t="n">
+        <v>337.94</v>
+      </c>
+      <c r="J713" t="n">
+        <v>339.64</v>
+      </c>
+      <c r="K713" t="n">
+        <v>347.78</v>
+      </c>
+      <c r="L713" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30258,7 +30384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B740"/>
+  <dimension ref="A1:B743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37661,6 +37787,36 @@
       </c>
       <c r="B740" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>
@@ -37829,28 +37985,28 @@
         <v>0.1115</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.33610473529806</v>
+        <v>-1.406744624666974</v>
       </c>
       <c r="J2" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="K2" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0274700232836772</v>
+        <v>0.03037599467419949</v>
       </c>
       <c r="M2" t="n">
-        <v>47.88859997199668</v>
+        <v>47.99226433659805</v>
       </c>
       <c r="N2" t="n">
-        <v>3006.725235056258</v>
+        <v>3019.823045158877</v>
       </c>
       <c r="O2" t="n">
-        <v>54.8336140980718</v>
+        <v>54.95291662103912</v>
       </c>
       <c r="P2" t="n">
-        <v>281.7641201509576</v>
+        <v>282.6308483044971</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37907,28 +38063,28 @@
         <v>0.0825</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.384813945050798</v>
+        <v>-0.3941077465122835</v>
       </c>
       <c r="J3" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="K3" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1546857917304866</v>
+        <v>0.1606324941222778</v>
       </c>
       <c r="M3" t="n">
-        <v>5.032761038180118</v>
+        <v>5.061929333267286</v>
       </c>
       <c r="N3" t="n">
-        <v>40.25331530785397</v>
+        <v>40.56396768969974</v>
       </c>
       <c r="O3" t="n">
-        <v>6.344550047706612</v>
+        <v>6.368984824106565</v>
       </c>
       <c r="P3" t="n">
-        <v>336.0883477823325</v>
+        <v>336.1993769616473</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37985,28 +38141,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3910447456136834</v>
+        <v>-0.3924932166992711</v>
       </c>
       <c r="J4" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="K4" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1736663327541962</v>
+        <v>0.1759671945520821</v>
       </c>
       <c r="M4" t="n">
-        <v>4.766368676444427</v>
+        <v>4.753165446051706</v>
       </c>
       <c r="N4" t="n">
-        <v>36.19303733106343</v>
+        <v>36.05527712015974</v>
       </c>
       <c r="O4" t="n">
-        <v>6.016064937404136</v>
+        <v>6.004604659772344</v>
       </c>
       <c r="P4" t="n">
-        <v>327.1215790418112</v>
+        <v>327.1388705848033</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38063,28 +38219,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3184880175130588</v>
+        <v>-0.3201805298049907</v>
       </c>
       <c r="J5" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="K5" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1202354443888488</v>
+        <v>0.1222672734851845</v>
       </c>
       <c r="M5" t="n">
-        <v>4.837523299612479</v>
+        <v>4.825425278564097</v>
       </c>
       <c r="N5" t="n">
-        <v>36.91921433258288</v>
+        <v>36.7818557701468</v>
       </c>
       <c r="O5" t="n">
-        <v>6.076118360646283</v>
+        <v>6.064804676998823</v>
       </c>
       <c r="P5" t="n">
-        <v>326.3530859850183</v>
+        <v>326.3732939973465</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38141,28 +38297,28 @@
         <v>0.0944</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3576247360566228</v>
+        <v>-0.3608192591831765</v>
       </c>
       <c r="J6" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="K6" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1976454838529071</v>
+        <v>0.2015626277037105</v>
       </c>
       <c r="M6" t="n">
-        <v>4.104313191302175</v>
+        <v>4.102536404095408</v>
       </c>
       <c r="N6" t="n">
-        <v>25.82657488953532</v>
+        <v>25.77519750221718</v>
       </c>
       <c r="O6" t="n">
-        <v>5.081985329527754</v>
+        <v>5.076927959132095</v>
       </c>
       <c r="P6" t="n">
-        <v>333.3614728230672</v>
+        <v>333.3996283668969</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38219,28 +38375,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.239389140703502</v>
+        <v>-0.2418877860743092</v>
       </c>
       <c r="J7" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="K7" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1491706831037481</v>
+        <v>0.1527039778269572</v>
       </c>
       <c r="M7" t="n">
-        <v>3.223951531259045</v>
+        <v>3.221456938768228</v>
       </c>
       <c r="N7" t="n">
-        <v>16.25923718002112</v>
+        <v>16.22573698582254</v>
       </c>
       <c r="O7" t="n">
-        <v>4.032274442547421</v>
+        <v>4.028118293424678</v>
       </c>
       <c r="P7" t="n">
-        <v>336.09551395969</v>
+        <v>336.1253586643647</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38297,28 +38453,28 @@
         <v>0.1156</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1113978058471085</v>
+        <v>-0.1154809691001734</v>
       </c>
       <c r="J8" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="K8" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05109728752277565</v>
+        <v>0.05474795798294296</v>
       </c>
       <c r="M8" t="n">
-        <v>2.73882608208078</v>
+        <v>2.745229313696502</v>
       </c>
       <c r="N8" t="n">
-        <v>11.46329378012631</v>
+        <v>11.50779916655289</v>
       </c>
       <c r="O8" t="n">
-        <v>3.385748629199502</v>
+        <v>3.392314721035313</v>
       </c>
       <c r="P8" t="n">
-        <v>337.0795192228656</v>
+        <v>337.1282937162127</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38375,28 +38531,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06385586571209907</v>
+        <v>-0.06502549855325175</v>
       </c>
       <c r="J9" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="K9" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01564593640574641</v>
+        <v>0.01634880048935028</v>
       </c>
       <c r="M9" t="n">
-        <v>2.851826036922729</v>
+        <v>2.846043679172729</v>
       </c>
       <c r="N9" t="n">
-        <v>12.7609697550901</v>
+        <v>12.7149409817527</v>
       </c>
       <c r="O9" t="n">
-        <v>3.57224995697251</v>
+        <v>3.565801590351418</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1749763508209</v>
+        <v>341.1889482806671</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38453,28 +38609,28 @@
         <v>0.1026</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04242260644738505</v>
+        <v>0.04074336036874495</v>
       </c>
       <c r="J10" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="K10" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00928765091721051</v>
+        <v>0.008635524008392514</v>
       </c>
       <c r="M10" t="n">
-        <v>2.471200340158814</v>
+        <v>2.468779648137508</v>
       </c>
       <c r="N10" t="n">
-        <v>9.549237527810224</v>
+        <v>9.524673178705275</v>
       </c>
       <c r="O10" t="n">
-        <v>3.090184060506789</v>
+        <v>3.086206924155487</v>
       </c>
       <c r="P10" t="n">
-        <v>340.5286029004625</v>
+        <v>340.5486639452567</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38531,28 +38687,28 @@
         <v>0.1391</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07441575316578446</v>
+        <v>0.07632739787989698</v>
       </c>
       <c r="J11" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="K11" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0300737881939428</v>
+        <v>0.0317932008297338</v>
       </c>
       <c r="M11" t="n">
-        <v>2.388813489949528</v>
+        <v>2.38810201199679</v>
       </c>
       <c r="N11" t="n">
-        <v>8.884083462878255</v>
+        <v>8.867200405626248</v>
       </c>
       <c r="O11" t="n">
-        <v>2.980617966609987</v>
+        <v>2.977784479378292</v>
       </c>
       <c r="P11" t="n">
-        <v>343.8133766897675</v>
+        <v>343.7905400971314</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38590,7 +38746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L710"/>
+  <dimension ref="A1:L713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82565,6 +82721,192 @@
         </is>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>-45.529278768528194,170.75977050101818</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>-45.53077693161778,170.75968729178092</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>-45.53129768196889,170.75911190366813</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>-45.53172557992283,170.75851472521504</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>-45.53217496743091,170.75788851468738</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>-45.53265733616208,170.75729160395088</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>-45.533126239401085,170.75668369924256</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>-45.533643858239074,170.75615054201566</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>-45.53416086974534,170.75563659444978</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>-45.53472031443641,170.7552076852045</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>-45.529226789071046,170.75973614254175</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>-45.53076860749214,170.75967770988356</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>-45.5313090819243,170.75913020131114</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>-45.53173543534,170.75852746736044</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>-45.53217967627041,170.7578944662089</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>-45.53266079881105,170.7572962693259</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>-45.53312731759708,170.75668524301548</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>-45.533645972617585,170.75615403358083</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>-45.53416086974534,170.75563659444978</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>-45.534722584825076,170.75521214286402</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>-45.52927958453215,170.75977104039822</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>-45.53077266462909,170.7596823800517</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>-45.53130735104121,170.7591274231345</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>-45.53173610124651,170.7585283283164</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>-45.532181492537,170.75789676179608</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>-45.53266138680802,170.75729706155948</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>-45.53312979110548,170.7566887846124</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>-45.5336435645754,170.75615005707607</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>-45.534160063736444,170.7556350541139</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>-45.53471941684086,170.75520592287413</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
